--- a/InputData/bldgs/SYDEC/Start Year Distributed Electricity Capacity.xlsx
+++ b/InputData/bldgs/SYDEC/Start Year Distributed Electricity Capacity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\bldgs\SYDEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\SYDEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A578AD3-D476-4117-8DCD-4CF8A8F12148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0546D8-EB11-462E-A675-5DDAC1A4C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="1004">
   <si>
     <t>Sources:</t>
   </si>
@@ -3133,6 +3133,15 @@
   </si>
   <si>
     <t>SYDEC Start Year Distributed Electricity Capacity</t>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. Behind-the-meter gas at data centers is counted from the first model year onward (BDESC), so start-year distributed capacity at data centers is zero.</t>
   </si>
 </sst>
 </file>
@@ -3781,7 +3790,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3932,6 +3941,11 @@
     <xf numFmtId="0" fontId="28" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3995,10 +4009,8 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="60% - Accent1 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
@@ -11796,7 +11808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
@@ -12093,6 +12105,14 @@
       </c>
       <c r="D47" t="s">
         <v>976</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B49" s="99" t="s">
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -23678,21 +23698,21 @@
       </c>
     </row>
     <row r="9" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="87"/>
-      <c r="C9" s="89" t="s">
+      <c r="B9" s="90"/>
+      <c r="C9" s="92" t="s">
         <v>979</v>
       </c>
-      <c r="D9" s="89"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="91" t="s">
+      <c r="D9" s="92"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="94" t="s">
         <v>980</v>
       </c>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="89"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
     </row>
     <row r="10" spans="2:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="88"/>
+      <c r="B10" s="91"/>
       <c r="C10" s="66">
         <v>2024</v>
       </c>
@@ -23716,16 +23736,16 @@
       </c>
     </row>
     <row r="11" spans="2:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="95" t="s">
         <v>981</v>
       </c>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
     </row>
     <row r="12" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="68" t="s">
@@ -31887,27 +31907,30 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>548</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="72" t="s">
         <v>998</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="72" t="s">
         <v>999</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="72" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>527</v>
       </c>
@@ -31920,8 +31943,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>599</v>
       </c>
@@ -31934,8 +31960,11 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>600</v>
       </c>
@@ -31945,12 +31974,15 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" s="97">
+      <c r="D4" s="73">
         <f>'BDESC-commercial'!B4</f>
         <v>13468.725</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>530</v>
       </c>
@@ -31963,8 +31995,11 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>531</v>
       </c>
@@ -31977,42 +32012,51 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>533</v>
       </c>
-      <c r="B7" s="97">
+      <c r="B7" s="73">
         <f>'BDESC-urban-residential'!B7</f>
         <v>250.57474912976602</v>
       </c>
-      <c r="C7" s="97">
+      <c r="C7" s="73">
         <f>'BDESC-rural-residential'!B7</f>
         <v>57.60425087023394</v>
       </c>
-      <c r="D7" s="97">
+      <c r="D7" s="73">
         <f>'BDESC-commercial'!B7</f>
         <v>585.6400000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>535</v>
       </c>
-      <c r="B8" s="98">
+      <c r="B8" s="74">
         <f>'BDESC-urban-residential'!B8</f>
         <v>30362.289170242049</v>
       </c>
-      <c r="C8" s="97">
+      <c r="C8" s="73">
         <f>'BDESC-rural-residential'!B8</f>
         <v>6979.940829757953</v>
       </c>
-      <c r="D8" s="97">
+      <c r="D8" s="73">
         <f>'BDESC-commercial'!B8</f>
         <v>21769.497000000003</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>536</v>
       </c>
@@ -32025,8 +32069,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>537</v>
       </c>
@@ -32039,8 +32086,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>538</v>
       </c>
@@ -32053,8 +32103,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>539</v>
       </c>
@@ -32064,12 +32117,15 @@
       <c r="C12">
         <v>0</v>
       </c>
-      <c r="D12" s="97">
+      <c r="D12" s="73">
         <f>'BDESC-commercial'!B12</f>
         <v>20.507000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>540</v>
       </c>
@@ -32082,8 +32138,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>541</v>
       </c>
@@ -32096,8 +32155,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>542</v>
       </c>
@@ -32110,8 +32172,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>543</v>
       </c>
@@ -32124,8 +32189,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>544</v>
       </c>
@@ -32138,8 +32206,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>545</v>
       </c>
@@ -32152,8 +32223,11 @@
       <c r="D18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>601</v>
       </c>
@@ -32166,8 +32240,11 @@
       <c r="D19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>602</v>
       </c>
@@ -32180,8 +32257,11 @@
       <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>603</v>
       </c>
@@ -32194,8 +32274,11 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>604</v>
       </c>
@@ -32208,8 +32291,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>605</v>
       </c>
@@ -32222,8 +32308,11 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="54" t="s">
         <v>606</v>
       </c>
@@ -32236,8 +32325,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="54" t="s">
         <v>607</v>
       </c>
@@ -32248,6 +32340,9 @@
         <v>0</v>
       </c>
       <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
     </row>
@@ -32271,105 +32366,105 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="76" t="s">
         <v>958</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
     </row>
     <row r="2" spans="1:21" ht="39" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
         <v>957</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="77" t="s">
         <v>956</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="74" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="77" t="s">
         <v>955</v>
       </c>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="74" t="s">
+      <c r="Q2" s="79"/>
+      <c r="R2" s="77" t="s">
         <v>954</v>
       </c>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="76"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="79"/>
     </row>
     <row r="3" spans="1:21" ht="39" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
         <v>953</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="74" t="s">
+      <c r="C3" s="79"/>
+      <c r="D3" s="77" t="s">
         <v>952</v>
       </c>
-      <c r="E3" s="76"/>
-      <c r="F3" s="74" t="s">
+      <c r="E3" s="79"/>
+      <c r="F3" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="76"/>
-      <c r="H3" s="74" t="s">
+      <c r="G3" s="79"/>
+      <c r="H3" s="77" t="s">
         <v>951</v>
       </c>
-      <c r="I3" s="76"/>
-      <c r="J3" s="74" t="s">
+      <c r="I3" s="79"/>
+      <c r="J3" s="77" t="s">
         <v>950</v>
       </c>
-      <c r="K3" s="76"/>
-      <c r="L3" s="74" t="s">
+      <c r="K3" s="79"/>
+      <c r="L3" s="77" t="s">
         <v>949</v>
       </c>
-      <c r="M3" s="76"/>
-      <c r="N3" s="74" t="s">
+      <c r="M3" s="79"/>
+      <c r="N3" s="77" t="s">
         <v>948</v>
       </c>
-      <c r="O3" s="76"/>
-      <c r="P3" s="74" t="s">
+      <c r="O3" s="79"/>
+      <c r="P3" s="77" t="s">
         <v>947</v>
       </c>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="74" t="s">
+      <c r="Q3" s="79"/>
+      <c r="R3" s="77" t="s">
         <v>946</v>
       </c>
-      <c r="S3" s="76"/>
-      <c r="T3" s="74" t="s">
+      <c r="S3" s="79"/>
+      <c r="T3" s="77" t="s">
         <v>945</v>
       </c>
-      <c r="U3" s="76"/>
+      <c r="U3" s="79"/>
     </row>
     <row r="4" spans="1:21" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
@@ -36467,29 +36562,29 @@
       </c>
     </row>
     <row r="67" spans="1:21" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="72" t="s">
+      <c r="A67" s="75" t="s">
         <v>886</v>
       </c>
-      <c r="B67" s="72"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="72"/>
-      <c r="H67" s="72"/>
-      <c r="I67" s="72"/>
-      <c r="J67" s="72"/>
-      <c r="K67" s="72"/>
-      <c r="L67" s="72"/>
-      <c r="M67" s="72"/>
-      <c r="N67" s="72"/>
-      <c r="O67" s="72"/>
-      <c r="P67" s="72"/>
-      <c r="Q67" s="72"/>
-      <c r="R67" s="72"/>
-      <c r="S67" s="72"/>
-      <c r="T67" s="72"/>
-      <c r="U67" s="72"/>
+      <c r="B67" s="75"/>
+      <c r="C67" s="75"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="75"/>
+      <c r="I67" s="75"/>
+      <c r="J67" s="75"/>
+      <c r="K67" s="75"/>
+      <c r="L67" s="75"/>
+      <c r="M67" s="75"/>
+      <c r="N67" s="75"/>
+      <c r="O67" s="75"/>
+      <c r="P67" s="75"/>
+      <c r="Q67" s="75"/>
+      <c r="R67" s="75"/>
+      <c r="S67" s="75"/>
+      <c r="T67" s="75"/>
+      <c r="U67" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -49204,43 +49299,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="89" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="83"/>
+      <c r="B1" s="86"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="85" t="s">
         <v>369</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="80" t="s">
         <v>370</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" ht="23.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
       <c r="B4" s="19"/>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="82" t="s">
         <v>371</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="84"/>
     </row>
     <row r="5" spans="1:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20"/>
@@ -53761,15 +53856,15 @@
       <c r="G220" s="25"/>
     </row>
     <row r="221" spans="1:7" s="6" customFormat="1" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="84" t="s">
+      <c r="A221" s="87" t="s">
         <v>522</v>
       </c>
-      <c r="B221" s="85"/>
-      <c r="C221" s="85"/>
-      <c r="D221" s="85"/>
-      <c r="E221" s="85"/>
-      <c r="F221" s="85"/>
-      <c r="G221" s="85"/>
+      <c r="B221" s="88"/>
+      <c r="C221" s="88"/>
+      <c r="D221" s="88"/>
+      <c r="E221" s="88"/>
+      <c r="F221" s="88"/>
+      <c r="G221" s="88"/>
     </row>
     <row r="222" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
